--- a/side.xlsx
+++ b/side.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ss358115\Desktop\Keeperメニュー\Keeperメニュー\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:41000001_{426D4487-FCF7-1442-B71A-E7F33AB72CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:41000001_{03A51310-5CF6-E540-99B0-D1F608169D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="64">
   <si>
     <t>商品名</t>
   </si>
@@ -74,13 +74,7 @@
     <t>タッチパネルキーパー</t>
   </si>
   <si>
-    <t>4180</t>
-  </si>
-  <si>
     <t>レンズコーティング</t>
-  </si>
-  <si>
-    <t>9130</t>
   </si>
   <si>
     <t>ホイールクリーニング</t>
@@ -252,63 +246,82 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>ホイールクリーニング</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エンジンルーム　クリーン＆プロテクト</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アンダーコート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>フロント(リア・ルーフ）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ホイールコーティング　シングル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ホイールコーティング　ダブル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>アルカリブロックキーパー</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ホイールクリーニング</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>レンズコーティング+ヘッドライトクリーン＆プロテクト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>エンジンルーム　クリーン＆プロテクト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>メッキクリーニング</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>鉄粉取り</t>
-    <rPh sb="0" eb="3">
-      <t>テップント</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>花粉のシミ取り</t>
-    <rPh sb="0" eb="2">
-      <t>カフン</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>ト</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>アンダーコート</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>フロント(リア・ルーフ）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ホイールコーティング　シングル</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ホイールコーティング　ダブル</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>軽研磨</t>
-  </si>
-  <si>
-    <t>lL</t>
+  </si>
+  <si>
+    <t>ウインドウまわり</t>
+  </si>
+  <si>
+    <t>ルーフレール同時施工</t>
+  </si>
+  <si>
+    <t>白サビ取り</t>
+  </si>
+  <si>
+    <t>普通車</t>
+  </si>
+  <si>
+    <t>軽自動車</t>
+  </si>
+  <si>
+    <t>ヘッドライトのみ</t>
+  </si>
+  <si>
+    <t>バイザー（4枚）</t>
+  </si>
+  <si>
+    <t>ヘッドライトクリーン＆プロテクト+レンズコーティングセット</t>
+  </si>
+  <si>
+    <t>アンダーウォッシュ</t>
+  </si>
+  <si>
+    <t>洗車とセット</t>
+  </si>
+  <si>
+    <t>細密研磨</t>
+  </si>
+  <si>
+    <t>車種別見積</t>
+  </si>
+  <si>
+    <t>別途見積</t>
+  </si>
+  <si>
+    <t>Keeper部分施工</t>
+  </si>
+  <si>
+    <t>コーティング価格の15%</t>
+  </si>
+  <si>
+    <t>花粉オールクリア</t>
+  </si>
+  <si>
+    <t>コーティングメニューを選択</t>
   </si>
 </sst>
 </file>
@@ -661,7 +674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D106"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
   <cols>
     <col min="4" max="4" width="8.99609375" style="1"/>
@@ -749,7 +762,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
         <v>4</v>
@@ -760,7 +773,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
         <v>5</v>
@@ -771,7 +784,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
         <v>6</v>
@@ -782,7 +795,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
         <v>7</v>
@@ -793,7 +806,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
@@ -804,806 +817,1081 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A13" t="s">
-        <v>17</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D13" s="1">
-        <v>8480</v>
+        <v>7360</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" s="1">
-        <v>42800</v>
+        <v>8040</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" s="1">
-        <v>47300</v>
+        <v>8480</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" s="1">
-        <v>51900</v>
+        <v>9060</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" s="1">
-        <v>55300</v>
+        <v>9630</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="1">
-        <v>60800</v>
+        <v>11330</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
         <v>18</v>
       </c>
-      <c r="C19" t="s">
-        <v>9</v>
-      </c>
       <c r="D19" s="1">
-        <v>71100</v>
+        <v>6240</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>20</v>
-      </c>
       <c r="D20" s="1">
-        <v>6240</v>
+        <v>12150</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D21" s="1">
-        <v>12150</v>
+        <v>23790</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D22" s="1">
-        <v>23790</v>
+        <v>35740</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A23" t="s">
-        <v>19</v>
-      </c>
-      <c r="B23" t="s">
-        <v>23</v>
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>4</v>
       </c>
       <c r="D23" s="1">
-        <v>35740</v>
+        <v>42800</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A24" t="s">
-        <v>24</v>
-      </c>
-      <c r="B24" t="s">
-        <v>25</v>
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>5</v>
       </c>
       <c r="D24" s="1">
-        <v>6820</v>
+        <v>47300</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A25" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" t="s">
-        <v>26</v>
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
+        <v>6</v>
       </c>
       <c r="D25" s="1">
-        <v>10010</v>
+        <v>51900</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A26" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" t="s">
-        <v>27</v>
+        <v>16</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
       </c>
       <c r="D26" s="1">
-        <v>18700</v>
+        <v>55300</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A27" t="s">
-        <v>24</v>
-      </c>
-      <c r="B27" t="s">
-        <v>28</v>
+        <v>16</v>
+      </c>
+      <c r="C27" t="s">
+        <v>8</v>
       </c>
       <c r="D27" s="1">
-        <v>29700</v>
+        <v>60800</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>16</v>
+      </c>
+      <c r="C28" t="s">
+        <v>9</v>
       </c>
       <c r="D28" s="1">
-        <v>4180</v>
+        <v>71100</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B29" t="s">
-        <v>31</v>
-      </c>
-      <c r="C29" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D29" s="1">
-        <v>4070</v>
+        <v>6820</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" t="s">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D30" s="1">
-        <v>4070</v>
+        <v>10010</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A31" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="D31" s="1">
-        <v>4070</v>
+        <v>18700</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B32" t="s">
-        <v>31</v>
-      </c>
-      <c r="C32" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D32" s="1">
-        <v>4290</v>
+        <v>29700</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A33" t="s">
-        <v>30</v>
-      </c>
-      <c r="B33" t="s">
-        <v>31</v>
-      </c>
-      <c r="C33" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="D33" s="1">
-        <v>4290</v>
+        <v>4180</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A34" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B34" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C34" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D34" s="1">
-        <v>4290</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A35" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C35" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D35" s="1">
-        <v>8910</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A36" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C36" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D36" s="1">
-        <v>8910</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A37" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C37" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D37" s="1">
-        <v>8910</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A38" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C38" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D38" s="1">
-        <v>9790</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A39" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C39" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D39" s="1">
-        <v>9790</v>
+        <v>4290</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A40" t="s">
+        <v>28</v>
+      </c>
+      <c r="B40" t="s">
         <v>30</v>
       </c>
-      <c r="B40" t="s">
-        <v>32</v>
-      </c>
       <c r="C40" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D40" s="1">
-        <v>10670</v>
+        <v>8910</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A41" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B41" t="s">
-        <v>50</v>
+        <v>30</v>
+      </c>
+      <c r="C41" t="s">
+        <v>5</v>
       </c>
       <c r="D41" s="1">
-        <v>13970</v>
+        <v>8910</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A42" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B42" t="s">
-        <v>34</v>
+        <v>30</v>
+      </c>
+      <c r="C42" t="s">
+        <v>6</v>
       </c>
       <c r="D42" s="1">
-        <v>7040</v>
+        <v>8910</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A43" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C43" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D43" s="1">
-        <v>1870</v>
+        <v>9790</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A44" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C44" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D44" s="1">
-        <v>1870</v>
+        <v>9790</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A45" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C45" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D45" s="1">
-        <v>1870</v>
+        <v>10670</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A46" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B46" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="D46" s="1">
-        <v>2200</v>
+        <v>13970</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A47" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B47" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D47" s="1">
-        <v>2200</v>
+        <v>7040</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A48" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B48" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C48" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D48" s="1">
-        <v>2200</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A49" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B49" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C49" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D49" s="1">
-        <v>5170</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A50" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B50" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C50" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D50" s="1">
-        <v>5170</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A51" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B51" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C51" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D51" s="1">
-        <v>5170</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A52" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C52" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D52" s="1">
-        <v>6380</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A53" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C53" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D53" s="1">
-        <v>6380</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A54" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B54" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C54" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D54" s="1">
-        <v>7150</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A55" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="B55" t="s">
-        <v>36</v>
+        <v>30</v>
+      </c>
+      <c r="C55" t="s">
+        <v>5</v>
       </c>
       <c r="D55" s="1">
-        <v>11550</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A56" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="B56" t="s">
-        <v>37</v>
+        <v>30</v>
+      </c>
+      <c r="C56" t="s">
+        <v>6</v>
       </c>
       <c r="D56" s="1">
-        <v>13090</v>
+        <v>5170</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A57" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="B57" t="s">
-        <v>38</v>
+        <v>30</v>
+      </c>
+      <c r="C57" t="s">
+        <v>7</v>
       </c>
       <c r="D57" s="1">
-        <v>15400</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="B58" t="s">
-        <v>36</v>
+        <v>30</v>
+      </c>
+      <c r="C58" t="s">
+        <v>8</v>
       </c>
       <c r="D58" s="1">
-        <v>17160</v>
+        <v>6380</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A59" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="B59" t="s">
-        <v>37</v>
+        <v>30</v>
+      </c>
+      <c r="C59" t="s">
+        <v>9</v>
       </c>
       <c r="D59" s="1">
-        <v>19580</v>
+        <v>7150</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A60" t="s">
-        <v>52</v>
-      </c>
-      <c r="B60" t="s">
-        <v>38</v>
+        <v>13</v>
+      </c>
+      <c r="C60" t="s">
+        <v>4</v>
       </c>
       <c r="D60" s="1">
-        <v>23210</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A61" t="s">
-        <v>39</v>
-      </c>
-      <c r="B61" t="s">
-        <v>36</v>
+        <v>13</v>
+      </c>
+      <c r="C61" t="s">
+        <v>5</v>
       </c>
       <c r="D61" s="1">
-        <v>17160</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A62" t="s">
-        <v>39</v>
-      </c>
-      <c r="B62" t="s">
-        <v>37</v>
+        <v>13</v>
+      </c>
+      <c r="C62" t="s">
+        <v>6</v>
       </c>
       <c r="D62" s="1">
-        <v>19580</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A63" t="s">
-        <v>39</v>
-      </c>
-      <c r="B63" t="s">
-        <v>38</v>
+        <v>13</v>
+      </c>
+      <c r="C63" t="s">
+        <v>7</v>
       </c>
       <c r="D63" s="1">
-        <v>23210</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A64" t="s">
-        <v>40</v>
+        <v>13</v>
+      </c>
+      <c r="C64" t="s">
+        <v>8</v>
       </c>
       <c r="D64" s="1">
-        <v>9130</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A65" t="s">
-        <v>41</v>
+        <v>13</v>
+      </c>
+      <c r="C65" t="s">
+        <v>9</v>
       </c>
       <c r="D65" s="1">
-        <v>9570</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A66" t="s">
         <v>44</v>
       </c>
+      <c r="B66" t="s">
+        <v>34</v>
+      </c>
       <c r="D66" s="1">
-        <v>12540</v>
+        <v>11550</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A67" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="B67" t="s">
+        <v>35</v>
       </c>
       <c r="D67" s="1">
-        <v>37400</v>
+        <v>13090</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A68" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="B68" t="s">
+        <v>36</v>
       </c>
       <c r="D68" s="1">
-        <v>2420</v>
+        <v>15400</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A69" t="s">
         <v>45</v>
       </c>
+      <c r="B69" t="s">
+        <v>34</v>
+      </c>
       <c r="D69" s="1">
-        <v>5940</v>
+        <v>17160</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A70" t="s">
-        <v>46</v>
+        <v>45</v>
+      </c>
+      <c r="B70" t="s">
+        <v>35</v>
       </c>
       <c r="D70" s="1">
-        <v>6820</v>
+        <v>19580</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A71" t="s">
-        <v>47</v>
+        <v>45</v>
+      </c>
+      <c r="B71" t="s">
+        <v>36</v>
       </c>
       <c r="D71" s="1">
-        <v>3080</v>
+        <v>23210</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A72" t="s">
-        <v>48</v>
+        <v>37</v>
+      </c>
+      <c r="B72" t="s">
+        <v>34</v>
       </c>
       <c r="D72" s="1">
-        <v>2970</v>
+        <v>17160</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A73" t="s">
-        <v>49</v>
-      </c>
-      <c r="C73" t="s">
-        <v>5</v>
+        <v>37</v>
+      </c>
+      <c r="B73" t="s">
+        <v>35</v>
       </c>
       <c r="D73" s="1">
-        <v>18150</v>
+        <v>19580</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A74" t="s">
-        <v>49</v>
-      </c>
-      <c r="C74" t="s">
-        <v>6</v>
+        <v>37</v>
+      </c>
+      <c r="B74" t="s">
+        <v>36</v>
       </c>
       <c r="D74" s="1">
-        <v>18150</v>
+        <v>23210</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A75" t="s">
-        <v>49</v>
-      </c>
-      <c r="C75" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D75" s="1">
-        <v>21670</v>
+        <v>9130</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A76" t="s">
-        <v>49</v>
-      </c>
-      <c r="C76" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="D76" s="1">
-        <v>21670</v>
+        <v>9570</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A77" t="s">
-        <v>49</v>
-      </c>
-      <c r="C77" t="s">
-        <v>9</v>
+        <v>54</v>
+      </c>
+      <c r="B77" t="s">
+        <v>50</v>
       </c>
       <c r="D77" s="1">
-        <v>21670</v>
+        <v>12540</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A78" t="s">
-        <v>11</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>12</v>
+        <v>54</v>
+      </c>
+      <c r="B78" t="s">
+        <v>51</v>
+      </c>
+      <c r="D78" s="1">
+        <v>10890</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A79" t="s">
-        <v>13</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>14</v>
+        <v>46</v>
+      </c>
+      <c r="B79" t="s">
+        <v>47</v>
+      </c>
+      <c r="D79" s="1">
+        <v>37400</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.1">
+        <v>46</v>
+      </c>
+      <c r="B80" t="s">
+        <v>48</v>
+      </c>
+      <c r="D80" s="1">
+        <v>52580</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A81" t="s">
+        <v>40</v>
+      </c>
+      <c r="D81" s="1">
+        <v>2420</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A82" t="s">
+        <v>41</v>
+      </c>
+      <c r="D82" s="1">
+        <v>5940</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A83" t="s">
+        <v>41</v>
+      </c>
+      <c r="D83" s="1">
+        <v>6820</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A84" t="s">
+        <v>41</v>
+      </c>
+      <c r="D84" s="1">
+        <v>3080</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A85" t="s">
+        <v>41</v>
+      </c>
+      <c r="D85" s="1">
+        <v>2970</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A86" t="s">
+        <v>42</v>
+      </c>
+      <c r="C86" t="s">
+        <v>5</v>
+      </c>
+      <c r="D86" s="1">
+        <v>18150</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A87" t="s">
+        <v>42</v>
+      </c>
+      <c r="C87" t="s">
+        <v>6</v>
+      </c>
+      <c r="D87" s="1">
+        <v>18150</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A88" t="s">
+        <v>42</v>
+      </c>
+      <c r="C88" t="s">
+        <v>7</v>
+      </c>
+      <c r="D88" s="1">
+        <v>21670</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A89" t="s">
+        <v>42</v>
+      </c>
+      <c r="C89" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89" s="1">
+        <v>21670</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A90" t="s">
+        <v>42</v>
+      </c>
+      <c r="C90" t="s">
+        <v>9</v>
+      </c>
+      <c r="D90" s="1">
+        <v>21670</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A91" t="s">
+        <v>11</v>
+      </c>
+      <c r="D91" s="1">
+        <v>4180</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A92" t="s">
+        <v>12</v>
+      </c>
+      <c r="B92" t="s">
+        <v>50</v>
+      </c>
+      <c r="D92" s="1">
+        <v>9130</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A93" t="s">
+        <v>12</v>
+      </c>
+      <c r="B93" t="s">
+        <v>51</v>
+      </c>
+      <c r="D93" s="1">
+        <v>7370</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A94" t="s">
+        <v>12</v>
+      </c>
+      <c r="B94" t="s">
+        <v>52</v>
+      </c>
+      <c r="D94" s="1">
+        <v>5940</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A95" t="s">
+        <v>12</v>
+      </c>
+      <c r="B95" t="s">
         <v>53</v>
       </c>
-      <c r="C81" t="s">
+      <c r="D95" s="1">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A96" t="s">
+        <v>13</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A97" t="s">
+        <v>49</v>
+      </c>
+      <c r="B97" t="s">
+        <v>47</v>
+      </c>
+      <c r="D97" s="1">
+        <v>42790</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A98" t="s">
+        <v>49</v>
+      </c>
+      <c r="B98" t="s">
+        <v>48</v>
+      </c>
+      <c r="D98" s="1">
+        <v>62920</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A99" t="s">
+        <v>55</v>
+      </c>
+      <c r="B99" t="s">
+        <v>56</v>
+      </c>
+      <c r="D99" s="1">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A100" t="s">
+        <v>57</v>
+      </c>
+      <c r="C100" t="s">
+        <v>4</v>
+      </c>
+      <c r="D100" s="1">
+        <v>20130</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A101" t="s">
+        <v>57</v>
+      </c>
+      <c r="C101" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.1">
-      <c r="C82" t="s">
+      <c r="D101" s="1">
+        <v>22220</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A102" t="s">
+        <v>57</v>
+      </c>
+      <c r="C102" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.1">
-      <c r="C83" t="s">
+      <c r="D102" s="1">
+        <v>23980</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A103" t="s">
+        <v>57</v>
+      </c>
+      <c r="C103" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.1">
-      <c r="C84" t="s">
-        <v>54</v>
+      <c r="D103" s="1">
+        <v>25410</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A104" t="s">
+        <v>57</v>
+      </c>
+      <c r="C104" t="s">
+        <v>8</v>
+      </c>
+      <c r="D104" s="1">
+        <v>28050</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A105" t="s">
+        <v>57</v>
+      </c>
+      <c r="B105" t="s">
+        <v>58</v>
+      </c>
+      <c r="C105" t="s">
+        <v>9</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.1">
+      <c r="A106" t="s">
+        <v>60</v>
+      </c>
+      <c r="B106" t="s">
+        <v>61</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/side.xlsx
+++ b/side.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ss358115\Desktop\Keeperメニュー\Keeperメニュー\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:41000001_{03A51310-5CF6-E540-99B0-D1F608169D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:41000001_{B0B0035F-6CF0-B941-B478-93D498001ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="64">
   <si>
     <t>商品名</t>
   </si>
@@ -674,7 +674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D106"/>
+  <dimension ref="A1:D103"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
   <cols>
     <col min="4" max="4" width="8.99609375" style="1"/>
@@ -1644,26 +1644,35 @@
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A83" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="C83" t="s">
+        <v>5</v>
       </c>
       <c r="D83" s="1">
-        <v>6820</v>
+        <v>18150</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A84" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="C84" t="s">
+        <v>6</v>
       </c>
       <c r="D84" s="1">
-        <v>3080</v>
+        <v>18150</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A85" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="C85" t="s">
+        <v>7</v>
       </c>
       <c r="D85" s="1">
-        <v>2970</v>
+        <v>21670</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.1">
@@ -1671,10 +1680,10 @@
         <v>42</v>
       </c>
       <c r="C86" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D86" s="1">
-        <v>18150</v>
+        <v>21670</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.1">
@@ -1682,51 +1691,51 @@
         <v>42</v>
       </c>
       <c r="C87" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D87" s="1">
-        <v>18150</v>
+        <v>21670</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A88" t="s">
-        <v>42</v>
-      </c>
-      <c r="C88" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D88" s="1">
-        <v>21670</v>
+        <v>4180</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A89" t="s">
-        <v>42</v>
-      </c>
-      <c r="C89" t="s">
-        <v>8</v>
+        <v>12</v>
+      </c>
+      <c r="B89" t="s">
+        <v>50</v>
       </c>
       <c r="D89" s="1">
-        <v>21670</v>
+        <v>9130</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A90" t="s">
-        <v>42</v>
-      </c>
-      <c r="C90" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="B90" t="s">
+        <v>51</v>
       </c>
       <c r="D90" s="1">
-        <v>21670</v>
+        <v>7370</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A91" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="B91" t="s">
+        <v>52</v>
       </c>
       <c r="D91" s="1">
-        <v>4180</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.1">
@@ -1734,84 +1743,84 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D92" s="1">
-        <v>9130</v>
+        <v>4400</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A93" t="s">
-        <v>12</v>
-      </c>
-      <c r="B93" t="s">
-        <v>51</v>
-      </c>
-      <c r="D93" s="1">
-        <v>7370</v>
+        <v>13</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A94" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="B94" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="D94" s="1">
-        <v>5940</v>
+        <v>42790</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A95" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="B95" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D95" s="1">
-        <v>4400</v>
+        <v>62920</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A96" t="s">
-        <v>13</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>14</v>
+        <v>55</v>
+      </c>
+      <c r="B96" t="s">
+        <v>56</v>
+      </c>
+      <c r="D96" s="1">
+        <v>880</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A97" t="s">
-        <v>49</v>
-      </c>
-      <c r="B97" t="s">
-        <v>47</v>
+        <v>57</v>
+      </c>
+      <c r="C97" t="s">
+        <v>4</v>
       </c>
       <c r="D97" s="1">
-        <v>42790</v>
+        <v>20130</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A98" t="s">
-        <v>49</v>
-      </c>
-      <c r="B98" t="s">
-        <v>48</v>
+        <v>57</v>
+      </c>
+      <c r="C98" t="s">
+        <v>5</v>
       </c>
       <c r="D98" s="1">
-        <v>62920</v>
+        <v>22220</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A99" t="s">
-        <v>55</v>
-      </c>
-      <c r="B99" t="s">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="C99" t="s">
+        <v>6</v>
       </c>
       <c r="D99" s="1">
-        <v>880</v>
+        <v>23980</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.1">
@@ -1819,10 +1828,10 @@
         <v>57</v>
       </c>
       <c r="C100" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D100" s="1">
-        <v>20130</v>
+        <v>25410</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.1">
@@ -1830,67 +1839,34 @@
         <v>57</v>
       </c>
       <c r="C101" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D101" s="1">
-        <v>22220</v>
+        <v>28050</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A102" t="s">
         <v>57</v>
       </c>
+      <c r="B102" t="s">
+        <v>58</v>
+      </c>
       <c r="C102" t="s">
-        <v>6</v>
-      </c>
-      <c r="D102" s="1">
-        <v>23980</v>
+        <v>9</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A103" t="s">
-        <v>57</v>
-      </c>
-      <c r="C103" t="s">
-        <v>7</v>
-      </c>
-      <c r="D103" s="1">
-        <v>25410</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.1">
-      <c r="A104" t="s">
-        <v>57</v>
-      </c>
-      <c r="C104" t="s">
-        <v>8</v>
-      </c>
-      <c r="D104" s="1">
-        <v>28050</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.1">
-      <c r="A105" t="s">
-        <v>57</v>
-      </c>
-      <c r="B105" t="s">
-        <v>58</v>
-      </c>
-      <c r="C105" t="s">
-        <v>9</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.1">
-      <c r="A106" t="s">
         <v>60</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B103" t="s">
         <v>61</v>
       </c>
-      <c r="D106" s="1" t="s">
+      <c r="D103" s="1" t="s">
         <v>63</v>
       </c>
     </row>

--- a/side.xlsx
+++ b/side.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ss358115\Desktop\Keeperメニュー\Keeperメニュー\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:41000001_{B0B0035F-6CF0-B941-B478-93D498001ADB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:41000001_{B9516C79-26DE-B942-906C-4EE98D2C16FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="64">
   <si>
     <t>商品名</t>
   </si>
@@ -312,16 +312,7 @@
     <t>別途見積</t>
   </si>
   <si>
-    <t>Keeper部分施工</t>
-  </si>
-  <si>
-    <t>コーティング価格の15%</t>
-  </si>
-  <si>
     <t>花粉オールクリア</t>
-  </si>
-  <si>
-    <t>コーティングメニューを選択</t>
   </si>
 </sst>
 </file>
@@ -674,7 +665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D103"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.1"/>
   <cols>
     <col min="4" max="4" width="8.99609375" style="1"/>
@@ -817,7 +808,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
         <v>4</v>
@@ -828,7 +819,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
@@ -839,7 +830,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s">
         <v>6</v>
@@ -850,7 +841,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C16" t="s">
         <v>7</v>
@@ -861,7 +852,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C17" t="s">
         <v>8</v>
@@ -872,7 +863,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.1">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C18" t="s">
         <v>9</v>
@@ -1857,17 +1848,6 @@
       </c>
       <c r="D102" s="1" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.1">
-      <c r="A103" t="s">
-        <v>60</v>
-      </c>
-      <c r="B103" t="s">
-        <v>61</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
